--- a/artfynd/A 44635-2021 artfynd.xlsx
+++ b/artfynd/A 44635-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 44635-2021 artfynd.xlsx
+++ b/artfynd/A 44635-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -801,6 +801,229 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>129350461</v>
+      </c>
+      <c r="B3" t="n">
+        <v>91703</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>1503</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Gräddporing</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Sidera lenis</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>A 44635, Lörstad, Sm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>572152</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6406871</v>
+      </c>
+      <c r="S3" t="n">
+        <v>50</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Blackstad</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På sönderfallande mkt murken låga.</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>129350420</v>
+      </c>
+      <c r="B4" t="n">
+        <v>92215</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>898</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Blackticka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Steccherinum collabens</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Fr.) Vesterholt</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>A 44635, Lörstad, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>572152</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6406871</v>
+      </c>
+      <c r="S4" t="n">
+        <v>50</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Blackstad</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 44635-2021 artfynd.xlsx
+++ b/artfynd/A 44635-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -804,59 +804,55 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129350461</v>
+        <v>129374692</v>
       </c>
       <c r="B3" t="n">
-        <v>91703</v>
+        <v>91954</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1503</v>
+        <v>4217</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A 44635, Lörstad, Sm</t>
+          <t>A44635 Lörstad, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>572152</v>
+        <v>572190</v>
       </c>
       <c r="R3" t="n">
         <v>6406871</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -880,17 +876,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På sönderfallande mkt murken låga.</t>
+          <t>tallåga</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,22 +902,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129350420</v>
+        <v>129350461</v>
       </c>
       <c r="B4" t="n">
-        <v>92215</v>
+        <v>91704</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -929,21 +925,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>898</v>
+        <v>1503</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1002,6 +998,11 @@
           <t>2025-10-26</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På sönderfallande mkt murken låga.</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1024,6 +1025,335 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>129350420</v>
+      </c>
+      <c r="B5" t="n">
+        <v>91954</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>4217</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Blodticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Meruliopsis taxicola</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>A 44635, Lörstad, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>572152</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6406871</v>
+      </c>
+      <c r="S5" t="n">
+        <v>50</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Blackstad</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>129374368</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57724</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>A 44635, Lörstad, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>572116</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6406964</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Blackstad</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Bearbetat levande gran, myror</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>129374144</v>
+      </c>
+      <c r="B7" t="n">
+        <v>91704</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1503</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Gräddporing</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Sidera lenis</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>A44635 Lörstad, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>572158</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6406813</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Blackstad</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>mycket murken talgåva</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Stefan Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 44635-2021 artfynd.xlsx
+++ b/artfynd/A 44635-2021 artfynd.xlsx
@@ -804,55 +804,59 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129374692</v>
+        <v>129350461</v>
       </c>
       <c r="B3" t="n">
-        <v>91954</v>
+        <v>91712</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4217</v>
+        <v>1503</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A44635 Lörstad, Sm</t>
+          <t>A 44635, Lörstad, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>572190</v>
+        <v>572152</v>
       </c>
       <c r="R3" t="n">
         <v>6406871</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -876,17 +880,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>tallåga</t>
+          <t>På sönderfallande mkt murken låga.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,44 +906,44 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129350461</v>
+        <v>129350420</v>
       </c>
       <c r="B4" t="n">
-        <v>91704</v>
+        <v>91962</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1503</v>
+        <v>4217</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -996,11 +1000,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-26</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På sönderfallande mkt murken låga.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1028,45 +1027,42 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129350420</v>
+        <v>129374368</v>
       </c>
       <c r="B5" t="n">
-        <v>91954</v>
+        <v>57724</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4217</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1074,13 +1070,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>572152</v>
+        <v>572116</v>
       </c>
       <c r="R5" t="n">
-        <v>6406871</v>
+        <v>6406964</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1104,12 +1100,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Bearbetat levande gran, myror</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1118,7 +1119,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1130,63 +1130,62 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129374368</v>
+        <v>129374692</v>
       </c>
       <c r="B6" t="n">
-        <v>57724</v>
+        <v>91962</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>4217</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>A 44635, Lörstad, Sm</t>
+          <t>A44635 Lörstad, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>572116</v>
+        <v>572190</v>
       </c>
       <c r="R6" t="n">
-        <v>6406964</v>
+        <v>6406871</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1220,7 +1219,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Bearbetat levande gran, myror</t>
+          <t>tallåga</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1229,18 +1228,19 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1250,7 +1250,7 @@
         <v>129374144</v>
       </c>
       <c r="B7" t="n">
-        <v>91704</v>
+        <v>91712</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 44635-2021 artfynd.xlsx
+++ b/artfynd/A 44635-2021 artfynd.xlsx
@@ -807,7 +807,7 @@
         <v>129350461</v>
       </c>
       <c r="B3" t="n">
-        <v>91712</v>
+        <v>91713</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -921,7 +921,7 @@
         <v>129350420</v>
       </c>
       <c r="B4" t="n">
-        <v>91962</v>
+        <v>91963</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1140,7 +1140,7 @@
         <v>129374692</v>
       </c>
       <c r="B6" t="n">
-        <v>91962</v>
+        <v>91963</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
         <v>129374144</v>
       </c>
       <c r="B7" t="n">
-        <v>91712</v>
+        <v>91713</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 44635-2021 artfynd.xlsx
+++ b/artfynd/A 44635-2021 artfynd.xlsx
@@ -1130,7 +1130,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 44635-2021 artfynd.xlsx
+++ b/artfynd/A 44635-2021 artfynd.xlsx
@@ -807,7 +807,7 @@
         <v>129350461</v>
       </c>
       <c r="B3" t="n">
-        <v>91713</v>
+        <v>91716</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -921,7 +921,7 @@
         <v>129350420</v>
       </c>
       <c r="B4" t="n">
-        <v>91963</v>
+        <v>91966</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>129374692</v>
       </c>
       <c r="B6" t="n">
-        <v>91963</v>
+        <v>91966</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
         <v>129374144</v>
       </c>
       <c r="B7" t="n">
-        <v>91713</v>
+        <v>91716</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 44635-2021 artfynd.xlsx
+++ b/artfynd/A 44635-2021 artfynd.xlsx
@@ -807,7 +807,7 @@
         <v>129350461</v>
       </c>
       <c r="B3" t="n">
-        <v>91716</v>
+        <v>91718</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -921,7 +921,7 @@
         <v>129350420</v>
       </c>
       <c r="B4" t="n">
-        <v>91966</v>
+        <v>91968</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1140,7 +1140,7 @@
         <v>129374692</v>
       </c>
       <c r="B6" t="n">
-        <v>91966</v>
+        <v>91968</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
         <v>129374144</v>
       </c>
       <c r="B7" t="n">
-        <v>91716</v>
+        <v>91718</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 44635-2021 artfynd.xlsx
+++ b/artfynd/A 44635-2021 artfynd.xlsx
@@ -807,7 +807,7 @@
         <v>129350461</v>
       </c>
       <c r="B3" t="n">
-        <v>91718</v>
+        <v>91722</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -921,7 +921,7 @@
         <v>129350420</v>
       </c>
       <c r="B4" t="n">
-        <v>91968</v>
+        <v>91972</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1140,7 +1140,7 @@
         <v>129374692</v>
       </c>
       <c r="B6" t="n">
-        <v>91968</v>
+        <v>91972</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
         <v>129374144</v>
       </c>
       <c r="B7" t="n">
-        <v>91718</v>
+        <v>91722</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 44635-2021 artfynd.xlsx
+++ b/artfynd/A 44635-2021 artfynd.xlsx
@@ -807,7 +807,7 @@
         <v>129350461</v>
       </c>
       <c r="B3" t="n">
-        <v>91722</v>
+        <v>91723</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -921,7 +921,7 @@
         <v>129350420</v>
       </c>
       <c r="B4" t="n">
-        <v>91972</v>
+        <v>91973</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1140,7 +1140,7 @@
         <v>129374692</v>
       </c>
       <c r="B6" t="n">
-        <v>91972</v>
+        <v>91973</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
         <v>129374144</v>
       </c>
       <c r="B7" t="n">
-        <v>91722</v>
+        <v>91723</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 44635-2021 artfynd.xlsx
+++ b/artfynd/A 44635-2021 artfynd.xlsx
@@ -807,7 +807,7 @@
         <v>129350461</v>
       </c>
       <c r="B3" t="n">
-        <v>91723</v>
+        <v>91726</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -921,7 +921,7 @@
         <v>129350420</v>
       </c>
       <c r="B4" t="n">
-        <v>91973</v>
+        <v>91976</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>129374692</v>
       </c>
       <c r="B6" t="n">
-        <v>91973</v>
+        <v>91976</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
         <v>129374144</v>
       </c>
       <c r="B7" t="n">
-        <v>91723</v>
+        <v>91726</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 44635-2021 artfynd.xlsx
+++ b/artfynd/A 44635-2021 artfynd.xlsx
@@ -807,7 +807,7 @@
         <v>129350461</v>
       </c>
       <c r="B3" t="n">
-        <v>91726</v>
+        <v>91754</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -921,7 +921,7 @@
         <v>129350420</v>
       </c>
       <c r="B4" t="n">
-        <v>91976</v>
+        <v>92004</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>129374368</v>
       </c>
       <c r="B5" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>129374692</v>
       </c>
       <c r="B6" t="n">
-        <v>91976</v>
+        <v>92004</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
         <v>129374144</v>
       </c>
       <c r="B7" t="n">
-        <v>91726</v>
+        <v>91754</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 44635-2021 artfynd.xlsx
+++ b/artfynd/A 44635-2021 artfynd.xlsx
@@ -807,7 +807,7 @@
         <v>129350461</v>
       </c>
       <c r="B3" t="n">
-        <v>91754</v>
+        <v>91760</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -921,7 +921,7 @@
         <v>129350420</v>
       </c>
       <c r="B4" t="n">
-        <v>92004</v>
+        <v>92010</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>129374368</v>
       </c>
       <c r="B5" t="n">
-        <v>57727</v>
+        <v>57732</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>129374692</v>
       </c>
       <c r="B6" t="n">
-        <v>92004</v>
+        <v>92010</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
         <v>129374144</v>
       </c>
       <c r="B7" t="n">
-        <v>91754</v>
+        <v>91760</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 44635-2021 artfynd.xlsx
+++ b/artfynd/A 44635-2021 artfynd.xlsx
@@ -807,7 +807,7 @@
         <v>129350461</v>
       </c>
       <c r="B3" t="n">
-        <v>91760</v>
+        <v>91761</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -921,7 +921,7 @@
         <v>129350420</v>
       </c>
       <c r="B4" t="n">
-        <v>92010</v>
+        <v>92011</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>129374368</v>
       </c>
       <c r="B5" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>129374692</v>
       </c>
       <c r="B6" t="n">
-        <v>92010</v>
+        <v>92011</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
         <v>129374144</v>
       </c>
       <c r="B7" t="n">
-        <v>91760</v>
+        <v>91761</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 44635-2021 artfynd.xlsx
+++ b/artfynd/A 44635-2021 artfynd.xlsx
@@ -807,7 +807,7 @@
         <v>129350461</v>
       </c>
       <c r="B3" t="n">
-        <v>91761</v>
+        <v>91766</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -921,7 +921,7 @@
         <v>129350420</v>
       </c>
       <c r="B4" t="n">
-        <v>92011</v>
+        <v>92016</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>129374692</v>
       </c>
       <c r="B6" t="n">
-        <v>92011</v>
+        <v>92016</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
         <v>129374144</v>
       </c>
       <c r="B7" t="n">
-        <v>91761</v>
+        <v>91766</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 44635-2021 artfynd.xlsx
+++ b/artfynd/A 44635-2021 artfynd.xlsx
@@ -1240,7 +1240,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 44635-2021 artfynd.xlsx
+++ b/artfynd/A 44635-2021 artfynd.xlsx
@@ -1140,7 +1140,7 @@
         <v>129374692</v>
       </c>
       <c r="B6" t="n">
-        <v>92016</v>
+        <v>92020</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand</t>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1250,7 +1250,7 @@
         <v>129374144</v>
       </c>
       <c r="B7" t="n">
-        <v>91766</v>
+        <v>91770</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
